--- a/Data/Raw/Regions_of_VietNam.xlsx
+++ b/Data/Raw/Regions_of_VietNam.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPT Polytechnic\Test_Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPT Polytechnic\Graduation_Project\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D4C1B1-7B86-45BF-AE88-F1E8F8D29FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0CFCFF-865A-4739-910B-F3DEF7053FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F7833C50-5068-4DBE-A8B6-6151336CFEE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$68</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="70">
-  <si>
-    <t>Bắc Bộ</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="71">
   <si>
     <t>Hà Nội</t>
   </si>
@@ -50,15 +50,6 @@
     <t>Tây Nguyên</t>
   </si>
   <si>
-    <t>Miền Tây</t>
-  </si>
-  <si>
-    <t>Miền Nam</t>
-  </si>
-  <si>
-    <t>Miền Trung</t>
-  </si>
-  <si>
     <t>Regions</t>
   </si>
   <si>
@@ -246,6 +237,21 @@
   </si>
   <si>
     <t>Thanh Hoá</t>
+  </si>
+  <si>
+    <t>Đồng bằng sông Cửu Long</t>
+  </si>
+  <si>
+    <t>Đông Nam Bộ</t>
+  </si>
+  <si>
+    <t>Đồng bằng sông Hồng</t>
+  </si>
+  <si>
+    <t>Trung du và miền núi phía Bắc</t>
+  </si>
+  <si>
+    <t>Duyên hải miền Trung</t>
   </si>
 </sst>
 </file>
@@ -295,7 +301,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -338,22 +344,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -364,11 +359,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -709,7 +703,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" customWidth="1"/>
     <col min="5" max="5" width="19.6640625" customWidth="1"/>
@@ -717,10 +711,10 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C1"/>
       <c r="G1" s="7"/>
@@ -732,25 +726,25 @@
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C2"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C3"/>
       <c r="G3" s="2"/>
@@ -762,10 +756,10 @@
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C4"/>
       <c r="G4" s="2"/>
@@ -777,10 +771,10 @@
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C5"/>
       <c r="G5" s="2"/>
@@ -792,10 +786,10 @@
     </row>
     <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C6"/>
       <c r="G6" s="2"/>
@@ -807,10 +801,10 @@
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C7"/>
       <c r="G7" s="2"/>
@@ -822,10 +816,10 @@
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C8"/>
       <c r="G8" s="2"/>
@@ -837,25 +831,25 @@
     </row>
     <row r="9" spans="1:12" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C10"/>
       <c r="G10" s="2"/>
@@ -867,10 +861,10 @@
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C11"/>
       <c r="G11" s="2"/>
@@ -882,10 +876,10 @@
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C12"/>
       <c r="G12" s="2"/>
@@ -897,10 +891,10 @@
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C13"/>
       <c r="G13" s="2"/>
@@ -912,10 +906,10 @@
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C14"/>
       <c r="G14" s="2"/>
@@ -927,10 +921,10 @@
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15"/>
       <c r="G15" s="2"/>
@@ -942,10 +936,10 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16"/>
       <c r="G16" s="2"/>
@@ -957,25 +951,25 @@
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C17"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C18"/>
       <c r="G18" s="2"/>
@@ -987,10 +981,10 @@
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C19"/>
       <c r="G19" s="2"/>
@@ -1002,10 +996,10 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20"/>
       <c r="G20" s="2"/>
@@ -1017,10 +1011,10 @@
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C21"/>
       <c r="G21" s="2"/>
@@ -1032,10 +1026,10 @@
     </row>
     <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C22"/>
       <c r="G22" s="2"/>
@@ -1047,10 +1041,10 @@
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C23"/>
       <c r="G23" s="2"/>
@@ -1062,10 +1056,10 @@
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C24"/>
       <c r="G24" s="2"/>
@@ -1077,10 +1071,10 @@
     </row>
     <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C25"/>
       <c r="G25" s="2"/>
@@ -1092,10 +1086,10 @@
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C26"/>
       <c r="G26" s="2"/>
@@ -1107,10 +1101,10 @@
     </row>
     <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C27"/>
       <c r="G27" s="2"/>
@@ -1122,334 +1116,334 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C28"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C29"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C30"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C31"/>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C33"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C34"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C35"/>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C37"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C38"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C39"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C40"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C41"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C42"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C43"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C44"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C45"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C46"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C47"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C48"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C49"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C50"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C51"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C52"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C53"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C54"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C55"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C56"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C57"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C58"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C59"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C60"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C61"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C62"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>6</v>
+      <c r="A63" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C63"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="C64"/>
     </row>
@@ -1466,18 +1460,19 @@
       <c r="C68"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B68" xr:uid="{48F4CE65-DF61-4860-8A2D-80B10BFCC964}"/>
   <mergeCells count="11">
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data/Raw/Regions_of_VietNam.xlsx
+++ b/Data/Raw/Regions_of_VietNam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FPT Polytechnic\Graduation_Project\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0CFCFF-865A-4739-910B-F3DEF7053FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8D547C-8030-445C-B40A-30FAEECCD14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F7833C50-5068-4DBE-A8B6-6151336CFEE1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="72">
   <si>
     <t>Hà Nội</t>
   </si>
@@ -251,7 +251,10 @@
     <t>Trung du và miền núi phía Bắc</t>
   </si>
   <si>
-    <t>Duyên hải miền Trung</t>
+    <t>Bắc Trung Bộ</t>
+  </si>
+  <si>
+    <t>Duyên hải Nam Trung Bộ</t>
   </si>
 </sst>
 </file>
@@ -359,10 +362,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -717,12 +720,12 @@
         <v>3</v>
       </c>
       <c r="C1"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
@@ -732,12 +735,12 @@
         <v>66</v>
       </c>
       <c r="C2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -837,19 +840,19 @@
         <v>67</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10"/>
       <c r="G10" s="2"/>
@@ -879,7 +882,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12"/>
       <c r="G12" s="2"/>
@@ -957,10 +960,10 @@
         <v>69</v>
       </c>
       <c r="C17"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
@@ -1137,7 +1140,7 @@
         <v>64</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30"/>
     </row>
@@ -1236,7 +1239,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41"/>
     </row>
@@ -1254,7 +1257,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43"/>
     </row>
@@ -1272,7 +1275,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45"/>
     </row>
@@ -1281,7 +1284,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46"/>
     </row>
@@ -1434,7 +1437,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63"/>
     </row>
@@ -1462,17 +1465,17 @@
   </sheetData>
   <autoFilter ref="B1:B68" xr:uid="{48F4CE65-DF61-4860-8A2D-80B10BFCC964}"/>
   <mergeCells count="11">
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
